--- a/BaoCao/9.1.TestCaseSprint1.xlsx
+++ b/BaoCao/9.1.TestCaseSprint1.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="657">
   <si>
     <t>TEST CASE SYSTEM SPRINT 1</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Tên dự án</t>
   </si>
   <si>
-    <t>SMARTTRIAL</t>
+    <t>SmartTrial</t>
   </si>
   <si>
     <t>STT</t>
@@ -97,7 +97,7 @@
     <t>Chưa kiểm tra</t>
   </si>
   <si>
-    <t>Bị chăn</t>
+    <t>Bị chặn</t>
   </si>
   <si>
     <t>Tổng số trường hợp thử nghiệm</t>
@@ -1559,7 +1559,7 @@
 2. Quan sát phần đầu trang</t>
   </si>
   <si>
-    <t>Đang ở trang chủ tìm gia sư (EduLink)</t>
+    <t>Đang ở trang chủ tìm gia sư (SmartTrial)</t>
   </si>
   <si>
     <t>Hiển thị nhãn "Nền tảng kết nối gia sư thông minh hàng đầu", tiêu đề lớn "Kết nối Gia sư chất lượng cao - Tối ưu lộ trình học với công nghệ AI &amp; Face ID" (cụm "AI &amp; Face ID" màu xanh) và đoạn mô tả bên dưới; chữ rõ ràng, không bị cắt</t>
@@ -1657,7 +1657,7 @@
 4. Nhấn "Tìm gia sư ngay"</t>
   </si>
   <si>
-    <t>Đang ở trang chủ tìm gia sư (EduLink); có gia sư phù hợp</t>
+    <t>Đang ở trang chủ tìm gia sư (SmartTrial); có gia sư phù hợp</t>
   </si>
   <si>
     <t>Các ô chọn hiển thị đúng giá trị đã chọn; hệ thống hiển thị danh sách/chuyển sang bước chọn thời gian với gia sư phù hợp tiêu chí</t>
@@ -1692,7 +1692,7 @@
 2. Nhấn "Tìm gia sư ngay"</t>
   </si>
   <si>
-    <t>Đang ở trang chủ tìm gia sư (EduLink); không có gia sư khớp tiêu chí</t>
+    <t>Đang ở trang chủ tìm gia sư (SmartTrial); không có gia sư khớp tiêu chí</t>
   </si>
   <si>
     <t>Hiển thị thông báo không tìm thấy gia sư phù hợp và gợi ý điều chỉnh tiêu chí</t>
@@ -2128,6 +2128,12 @@
   </si>
   <si>
     <t>Bảng lịch tải và hiển thị đầy đủ, chính xác trong thời gian hợp lý; không bị treo, giật lag hoặc hiển thị sai lệch dữ liệu Trống/Kín</t>
+  </si>
+  <si>
+    <t>GUI Show tìm kiếm giáo viên</t>
+  </si>
+  <si>
+    <t>FUNCTION show tìm kiếm giáo viên</t>
   </si>
 </sst>
 </file>
@@ -10161,7 +10167,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="12" t="s">
-        <v>469</v>
+        <v>655</v>
       </c>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -10451,7 +10457,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="12" t="s">
-        <v>500</v>
+        <v>656</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
